--- a/YER/Kashish_Taneja_Work_Summary.xlsx
+++ b/YER/Kashish_Taneja_Work_Summary.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kashtane\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kashtane\Documents\YER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FA651AA-6A02-4FB1-9D7E-825F9DB90976}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E7B07FD-7696-4D0D-8F38-CA6E8BEA57E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="846" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="846" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Executive Summary" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="328">
   <si>
     <t>Phase</t>
   </si>
@@ -826,13 +826,196 @@
   </si>
   <si>
     <t>AWS, Docker, Kubernetes, Python, GitHub, Bash, Power BI</t>
+  </si>
+  <si>
+    <t>DETAILS --&gt;</t>
+  </si>
+  <si>
+    <t>Learning Platform</t>
+  </si>
+  <si>
+    <t>The Complete Python Bootcamp From Zero to Hero in Python</t>
+  </si>
+  <si>
+    <t>Udemy</t>
+  </si>
+  <si>
+    <t>Python basics to advanced topics, OOP, files, modules, projects</t>
+  </si>
+  <si>
+    <t>Introduction to Git and GitHub Basics</t>
+  </si>
+  <si>
+    <t>Coursera</t>
+  </si>
+  <si>
+    <t>Git fundamentals, version control concepts</t>
+  </si>
+  <si>
+    <t>Power BI Masterclass from Scratch in 90 minutes [2026]</t>
+  </si>
+  <si>
+    <t>Power BI basics, data modeling, DAX fundamentals, dashboards, reports</t>
+  </si>
+  <si>
+    <t>Introduction to Continuous Integration &amp; Continuous Delivery</t>
+  </si>
+  <si>
+    <t>CI/CD concepts, pipelines, automation, DevOps practices</t>
+  </si>
+  <si>
+    <t>aws_cloud_beginnner_ocean_certificate</t>
+  </si>
+  <si>
+    <t>Capgemini</t>
+  </si>
+  <si>
+    <t>AWS cloud fundamentals, Capgemini-specific cloud enablement</t>
+  </si>
+  <si>
+    <t>aws_cloud_practitioner_ocean_certificate</t>
+  </si>
+  <si>
+    <t>Practice set AWS Certified Data Engineer - Associate certificate</t>
+  </si>
+  <si>
+    <t>AWS</t>
+  </si>
+  <si>
+    <t>Exam-focused practice questions covering data ingestion, storage, processing, analytics on AWS</t>
+  </si>
+  <si>
+    <t>Programming for everybody</t>
+  </si>
+  <si>
+    <t>Programming fundamentals, variables, loops, conditionals using Python</t>
+  </si>
+  <si>
+    <t>Python data structures</t>
+  </si>
+  <si>
+    <t>Lists, dictionaries, tuples, strings, files, data handling in Python</t>
+  </si>
+  <si>
+    <t>Advanced Git and GitHub Features</t>
+  </si>
+  <si>
+    <t>Advanced Git commands, branching strategies, collaboration workflows</t>
+  </si>
+  <si>
+    <t>Bash Scripting and Shell Programming (Linux Command Line)</t>
+  </si>
+  <si>
+    <t>Linux commands, shell scripting, automation, environment management</t>
+  </si>
+  <si>
+    <t>Git and GitHub Complete Master Class</t>
+  </si>
+  <si>
+    <t>Git basics, repositories, commits, branches, GitHub collaboration</t>
+  </si>
+  <si>
+    <t>Intermediate Git and GitHub Workflow</t>
+  </si>
+  <si>
+    <t>Advanced workflows, pull requests, conflict resolution, best practices</t>
+  </si>
+  <si>
+    <t>Kubernetes for the Absolute Beginners - Hands-on</t>
+  </si>
+  <si>
+    <t>Kubernetes fundamentals, cluster architecture, pods, services, deployments, namespaces, hands-on labs</t>
+  </si>
+  <si>
+    <t>Supervised ML- Regression and Classification</t>
+  </si>
+  <si>
+    <t>Supervised learning models, regression techniques, classification algorithms, evaluation metrics</t>
+  </si>
+  <si>
+    <t>Ultimate AWS Certified Cloud Practitioner CLF-C02 2026</t>
+  </si>
+  <si>
+    <t>AWS cloud concepts, core services, security, pricing, architecture</t>
+  </si>
+  <si>
+    <t>Docker for the Absolute Beginner - Hands On - DevOps</t>
+  </si>
+  <si>
+    <t>Docker fundamentals, container lifecycle, DevOps integration</t>
+  </si>
+  <si>
+    <t>Ultimate AWS Certified Solutions Architect Associate 2026</t>
+  </si>
+  <si>
+    <t>AWS architecture, compute, storage, networking, security, best practices</t>
+  </si>
+  <si>
+    <t>Global Insurance Industry L1 Certification</t>
+  </si>
+  <si>
+    <t>Degreed</t>
+  </si>
+  <si>
+    <t>Insurance industry fundamentals, products, value chain, terminology</t>
+  </si>
+  <si>
+    <t>Global Banking Industry L1 Certification</t>
+  </si>
+  <si>
+    <t>Banking concepts, products, operations, compliance basics</t>
+  </si>
+  <si>
+    <t>Global Insurance Industry L2 Certification</t>
+  </si>
+  <si>
+    <t>MyLearning Mandatory Trainings</t>
+  </si>
+  <si>
+    <t>Mandatory Compliance Trainings by Capgemini</t>
+  </si>
+  <si>
+    <t>Certification path</t>
+  </si>
+  <si>
+    <t>Completion_Date</t>
+  </si>
+  <si>
+    <t>Udemy Course Completion Certificate | Udemy</t>
+  </si>
+  <si>
+    <t>Coursera | Online Courses &amp; Credentials From Top Educators. Join for Free | Coursera</t>
+  </si>
+  <si>
+    <t>imp-data/certificates/Practice set AWS Certified Data Engineer - Associate certificate.pdf at main · tanejakashish05/imp-data</t>
+  </si>
+  <si>
+    <t>imp-data/certificates/aws_cloud_practitioner_ocean_certificate.pdf at main · tanejakashish05/imp-data</t>
+  </si>
+  <si>
+    <t>imp-data/certificates/aws_cloud_beginner_ocean_certificate.pdf at main · tanejakashish05/imp-data</t>
+  </si>
+  <si>
+    <t>Learning History – SAP SuccessFactors</t>
+  </si>
+  <si>
+    <t>imp-data/certificates/global insurance L2.pdf at main · tanejakashish05/imp-data</t>
+  </si>
+  <si>
+    <t>imp-data/certificates/global insurance L1.pdf at main · tanejakashish05/imp-data</t>
+  </si>
+  <si>
+    <t>imp-data/certificates/global banking L1.pdf at main · tanejakashish05/imp-data</t>
+  </si>
+  <si>
+    <t>Insurance industry in detail, products, value chain, terminology</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -863,6 +1046,35 @@
       <color rgb="FF000000"/>
       <name val="Segoe UI"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -916,10 +1128,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -942,8 +1155,16 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="17" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2210,134 +2431,571 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.90625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="53.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="88.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A1" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="8" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="C1" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>316</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="10" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="C2" s="10"/>
+      <c r="D2" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="F2" s="11">
+        <v>45597</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="10" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="C3" s="10"/>
+      <c r="D3" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="F3" s="11">
+        <v>45689</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="10" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+      <c r="C4" s="10"/>
+      <c r="D4" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="F4" s="11">
+        <v>45689</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="10" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+      <c r="C5" s="10"/>
+      <c r="D5" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="F5" s="11">
+        <v>45717</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="10" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+      <c r="C6" s="10"/>
+      <c r="D6" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="F6" s="11">
+        <v>45839</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>321</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="10" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+      <c r="C7" s="10"/>
+      <c r="D7" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="F7" s="11">
+        <v>45870</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>320</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="10" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+      <c r="C8" s="10"/>
+      <c r="D8" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="F8" s="11">
+        <v>45870</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="10" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+      <c r="C9" s="10"/>
+      <c r="D9" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="F9" s="11">
+        <v>45931</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="10" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+      <c r="C10" s="10"/>
+      <c r="D10" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="F10" s="11">
+        <v>46023</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="10" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+      <c r="C11" s="10"/>
+      <c r="D11" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="F11" s="11">
+        <v>46023</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="10" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+      <c r="C12" s="10"/>
+      <c r="D12" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="F12" s="11">
+        <v>46023</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="10" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
+      <c r="C13" s="10"/>
+      <c r="D13" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="F13" s="11">
+        <v>46023</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="10" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
+      <c r="C14" s="10"/>
+      <c r="D14" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="F14" s="11">
+        <v>46023</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="10" t="s">
         <v>251</v>
       </c>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="F15" s="11">
+        <v>46054</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16" s="10"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="F16" s="11">
+        <v>46054</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="H16" s="10" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A17" s="10"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="F17" s="11">
+        <v>46054</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A18" s="10"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="F18" s="11">
+        <v>46054</v>
+      </c>
+      <c r="G18" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="H18" s="10" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A19" s="10"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="F19" s="11">
+        <v>46113</v>
+      </c>
+      <c r="G19" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A20" s="10"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>309</v>
+      </c>
+      <c r="F20" s="11">
+        <v>46113</v>
+      </c>
+      <c r="G20" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="H20" s="10" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A21" s="10"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10" t="s">
+        <v>311</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>309</v>
+      </c>
+      <c r="F21" s="11">
+        <v>46113</v>
+      </c>
+      <c r="G21" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="H21" s="10" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A22" s="10"/>
+      <c r="B22" s="10"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>309</v>
+      </c>
+      <c r="F22" s="11">
+        <v>46113</v>
+      </c>
+      <c r="G22" s="12" t="s">
+        <v>324</v>
+      </c>
+      <c r="H22" s="10" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A23" s="10"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10" t="s">
+        <v>314</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>309</v>
+      </c>
+      <c r="F23" s="10"/>
+      <c r="G23" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A24" s="10"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="10"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A25" s="10"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="10"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1" display="https://www.udemy.com/certificate/UC-076bd9b1-c384-4c8d-bbdc-d3fd0024bd51/" xr:uid="{C5F337FB-3452-4517-B3F2-14BE62B6C124}"/>
+    <hyperlink ref="G3" r:id="rId2" display="https://www.udemy.com/certificate/UC-9fd61a16-73dd-4cf6-aeab-95baf6c6753f/" xr:uid="{5F2BF44E-69A5-46B3-8A01-39C13168E40A}"/>
+    <hyperlink ref="G10" r:id="rId3" display="https://www.udemy.com/certificate/UC-dbf72255-65ce-4973-8293-aae94642b92e/" xr:uid="{5630B4B9-F815-480A-8DA3-7754C11AB406}"/>
+    <hyperlink ref="G14" r:id="rId4" display="https://www.coursera.org/account/accomplishments/specialization/NTOU4F98CZI1" xr:uid="{3F7E4045-0FC9-401D-9610-871C59EC0F8F}"/>
+    <hyperlink ref="G11" r:id="rId5" display="https://www.coursera.org/account/accomplishments/certificate/3UPMSJCJOTHU" xr:uid="{C56458F3-5910-42A8-80D6-2948B23304B2}"/>
+    <hyperlink ref="G12" r:id="rId6" display="https://www.coursera.org/account/accomplishments/certificate/NEKEMS2FHB95" xr:uid="{0B78F4F4-36FE-4A99-ABCB-E231950C6D8E}"/>
+    <hyperlink ref="G13" r:id="rId7" display="https://www.coursera.org/account/accomplishments/certificate/OHQDU3KSL9CF" xr:uid="{A2A60A0A-5F03-4683-81E5-E58A9345CAD9}"/>
+    <hyperlink ref="G4" r:id="rId8" display="https://www.udemy.com/certificate/UC-59ac13b6-e477-4ecf-9730-d3808c2ad15a/" xr:uid="{2EEDAC20-F353-4914-A4A9-9D5262CF86E5}"/>
+    <hyperlink ref="G16" r:id="rId9" display="https://www.udemy.com/certificate/UC-1a1a4f0a-fdb3-4282-be01-79225989d70c/" xr:uid="{D5E82BF1-A386-4259-B537-DC7C01ACF8AA}"/>
+    <hyperlink ref="G18" r:id="rId10" display="https://www.udemy.com/certificate/UC-f4ad3d9c-499e-436c-89e3-4b354e38c2a7/" xr:uid="{B7F73173-C24F-49D0-909A-54A98DB2D156}"/>
+    <hyperlink ref="G17" r:id="rId11" display="https://www.udemy.com/certificate/UC-b3c7304c-0f92-428a-9b4a-687da8bcb324/" xr:uid="{6404C0A7-8CCB-49C6-B0CF-CCCB5D6BD41B}"/>
+    <hyperlink ref="G19" r:id="rId12" display="https://www.udemy.com/certificate/UC-4bfed102-7b94-40b1-953e-ecaef489e0fa/" xr:uid="{AEF53933-873E-4C12-BB84-C7FD96A00BDC}"/>
+    <hyperlink ref="G8" r:id="rId13" display="https://www.coursera.org/account/accomplishments/certificate/I6I5JHWCR9CA" xr:uid="{65562597-157A-4030-834E-60F87B190FF8}"/>
+    <hyperlink ref="G9" r:id="rId14" display="https://www.coursera.org/account/accomplishments/certificate/DEJFTT9C2VDY" xr:uid="{0A824F78-07CF-46D2-947E-E7FDE9D8ABC2}"/>
+    <hyperlink ref="G15" r:id="rId15" display="https://www.coursera.org/account/accomplishments/certificate/I66RP600T3QN" xr:uid="{E36E2668-530C-4012-AFFF-2B6B60715F4E}"/>
+    <hyperlink ref="G7" r:id="rId16" display="https://github.com/tanejakashish05/imp-data/blob/main/certificates/Practice set AWS Certified Data Engineer - Associate certificate.pdf" xr:uid="{1DDE5F37-7FC4-45FE-959C-94FF86EAF346}"/>
+    <hyperlink ref="G6" r:id="rId17" display="https://github.com/tanejakashish05/imp-data/blob/main/certificates/aws_cloud_practitioner_ocean_certificate.pdf" xr:uid="{39AA2D4D-4699-47C3-BBB3-2A517C522BEF}"/>
+    <hyperlink ref="G5" r:id="rId18" display="https://github.com/tanejakashish05/imp-data/blob/main/certificates/aws_cloud_beginner_ocean_certificate.pdf" xr:uid="{4F8520FC-DB42-48CF-BC26-87D28C21F58F}"/>
+    <hyperlink ref="G23" r:id="rId19" location="/history" display="https://capgemitec.plateau.com/learning/user/personal/viewCompletedWork.do - /history" xr:uid="{7E88186F-C4D9-4BE0-973C-79347C750A43}"/>
+    <hyperlink ref="G22" r:id="rId20" display="https://github.com/tanejakashish05/imp-data/blob/main/certificates/global insurance L2.pdf" xr:uid="{EA125911-A357-44FA-8C2D-3F4C2F67BE1F}"/>
+    <hyperlink ref="G21" r:id="rId21" display="https://github.com/tanejakashish05/imp-data/blob/main/certificates/global banking L1.pdf" xr:uid="{434C5B2C-71C1-4DBC-9882-1404F538EE0F}"/>
+    <hyperlink ref="G20" r:id="rId22" display="https://github.com/tanejakashish05/imp-data/blob/main/certificates/global insurance L1.pdf" xr:uid="{69784910-0ED6-4873-B881-5EBFC9AD9EA9}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
